--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7061B8-B5DC-4CD6-8C5E-01A095143CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318C5472-5ADB-41B8-831F-67CB9DACBE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 19-12-2025'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 29-01-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318C5472-5ADB-41B8-831F-67CB9DACBE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F7152D-C161-4C98-B2CC-A65092EC6158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 29-01-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 02-02-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F7152D-C161-4C98-B2CC-A65092EC6158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9FB1A-67E8-4D0B-8580-AC88525C7FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 02-02-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 20-02-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -404,9 +404,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,7 +429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -452,7 +452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9FB1A-67E8-4D0B-8580-AC88525C7FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DE3003-EF73-40B1-808B-C92120176ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 20-02-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 04-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DE3003-EF73-40B1-808B-C92120176ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C6FE0-ED27-4141-B4B9-978816392C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 04-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 06-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C6FE0-ED27-4141-B4B9-978816392C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A6D390-6BD0-4D40-82E0-25EDE4C86B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A6D390-6BD0-4D40-82E0-25EDE4C86B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC5D9E5-F868-4F60-A5DF-594DEC195CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC5D9E5-F868-4F60-A5DF-594DEC195CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB6AA18-D0B3-4890-8492-1CA2E5841D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 06-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 09-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB6AA18-D0B3-4890-8492-1CA2E5841D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B959650-7FC3-46BA-82C6-CAE5DFDB624D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B959650-7FC3-46BA-82C6-CAE5DFDB624D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C6DF44-ED8F-4B99-B62E-07FB2030E9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 09-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 11-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C6DF44-ED8F-4B99-B62E-07FB2030E9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD26FE-18D6-4870-95D0-D9E158FB56CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD26FE-18D6-4870-95D0-D9E158FB56CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A9BAFE-8C83-4222-B822-AE1DA32C511A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 11-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 20-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A9BAFE-8C83-4222-B822-AE1DA32C511A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980BA5EA-9998-4E43-AED9-2DB16CA67939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 20-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 25-03-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980BA5EA-9998-4E43-AED9-2DB16CA67939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C314BDF4-0FA8-4CF9-A5C5-04F7A7CCD6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 25-03-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 08-04-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C314BDF4-0FA8-4CF9-A5C5-04F7A7CCD6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B108D5B5-77B1-43C5-A70D-A7F9EBE81E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 08-04-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 10-04-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B108D5B5-77B1-43C5-A70D-A7F9EBE81E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD274B3-9A6A-4E82-952F-E569EA37F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD274B3-9A6A-4E82-952F-E569EA37F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACCB72D-E473-43D1-B27D-671A121E8ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 10-04-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 14-04-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACCB72D-E473-43D1-B27D-671A121E8ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABF5963-D577-4E11-915F-CA89D91DEB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 14-04-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 24-04-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABF5963-D577-4E11-915F-CA89D91DEB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E56FFC-61D4-48BF-91BC-005986A0A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E56FFC-61D4-48BF-91BC-005986A0A6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC02051-3A6E-48AB-B2AA-237A4BFD8A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 24-04-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 27-04-2026'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC02051-3A6E-48AB-B2AA-237A4BFD8A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B562799-970C-43F4-87A1-AC8F257866AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 27-04-2026'!$A$1:$G$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 06-05-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Standard</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>EG Dental (EG)</t>
+  </si>
+  <si>
+    <t>Nexta (Plandent)</t>
   </si>
   <si>
     <t>PC tandlægesystem (EDB totalløsninger)</t>
@@ -403,10 +406,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,42 +431,48 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B562799-970C-43F4-87A1-AC8F257866AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2938FF-97C7-4646-9AEF-93DC7F731DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 06-05-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 01-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2938FF-97C7-4646-9AEF-93DC7F731DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9819E2-50A5-4457-9FA6-6E1085527C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 01-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 02-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9819E2-50A5-4457-9FA6-6E1085527C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E55487-ED3A-4CF6-A420-484BC40AF26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E55487-ED3A-4CF6-A420-484BC40AF26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F09028D-FEB7-49A3-96E7-6DFF40F41BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 02-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 05-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318C5472-5ADB-41B8-831F-67CB9DACBE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55EA065-DC42-4E5D-A9EF-A5DDD9BA9955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F36766E-8C1E-4511-8F8C-D02218299F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEFB54C-A30B-4C91-9763-0D4F61B6973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEFB54C-A30B-4C91-9763-0D4F61B6973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49B0604-A6EB-4B72-988F-59F6C2AC187E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49B0604-A6EB-4B72-988F-59F6C2AC187E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6C9DEC-DFA9-45B2-A555-2D38D25B020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 09-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 15-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6C9DEC-DFA9-45B2-A555-2D38D25B020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFFA724-F808-4F0E-95E0-94301FA954C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 15-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 22-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFFA724-F808-4F0E-95E0-94301FA954C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86C0544-948A-411F-8371-EBD975591BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 22-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 23-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86C0544-948A-411F-8371-EBD975591BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4ED16CF-02F9-457B-AA9C-EFBAA24D0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFFA724-F808-4F0E-95E0-94301FA954C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59566D1F-6F6E-476A-8237-896697AB1A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 22-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 23-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59566D1F-6F6E-476A-8237-896697AB1A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50568671-9D52-4B28-9710-69C33F5AE7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 23-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 25-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50568671-9D52-4B28-9710-69C33F5AE7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAAB941-AC08-4813-9BE1-5C2464D5EAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 25-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 30-06-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAAB941-AC08-4813-9BE1-5C2464D5EAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2F76F4-F9FF-4B79-866E-2CE3BE808A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2F76F4-F9FF-4B79-866E-2CE3BE808A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73604AB3-FF1E-4305-A6C1-1BF5D9CB1CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 30-06-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 01-07-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73604AB3-FF1E-4305-A6C1-1BF5D9CB1CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841775F1-8105-490B-983A-B19F8438F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 01-07-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 02-07-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73604AB3-FF1E-4305-A6C1-1BF5D9CB1CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD601E21-2F8D-4606-B1EA-E1E8C7F613ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 01-07-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 03-07-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841775F1-8105-490B-983A-B19F8438F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEE1260-4CF6-412B-B39C-0166D68961ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 02-07-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 03-07-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEE1260-4CF6-412B-B39C-0166D68961ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37D5C00-BD2A-40B0-B5B8-86656876C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 03-07-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 09-07-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37D5C00-BD2A-40B0-B5B8-86656876C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD17F89A-845B-4DB9-AFF6-0FA64835311D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 09-07-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 19-08-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD17F89A-845B-4DB9-AFF6-0FA64835311D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C912D-AAE7-435E-8C27-94A30D02C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 19-08-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 21-08-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C912D-AAE7-435E-8C27-94A30D02C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087D7480-9F0A-4D49-A887-E602A7B19008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 21-08-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 27-08-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -407,9 +407,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087D7480-9F0A-4D49-A887-E602A7B19008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42F07E6-692F-49EE-B0B4-88C19286782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 27-08-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 02-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42F07E6-692F-49EE-B0B4-88C19286782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF2E3CB-CC49-4615-B95A-9DC55B473AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 02-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 06-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF2E3CB-CC49-4615-B95A-9DC55B473AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D9C389-162C-4EDF-BA11-D6963BA56BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D9C389-162C-4EDF-BA11-D6963BA56BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C2EFE6-D7DD-42F2-8D82-55D19B8FFFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 06-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 07-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C2EFE6-D7DD-42F2-8D82-55D19B8FFFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D2C61-E7DE-4211-9761-DC50F2F0B826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tandlægesystemer">'Opdateret d. 07-09-2026'!$A$1:$H$3</definedName>
+    <definedName name="Tandlægesystemer">'Opdateret d. 09-09-2026'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Tandlægesystemer_excel.XLSX
+++ b/html/Tandlægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D2C61-E7DE-4211-9761-DC50F2F0B826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76792FDD-22FD-4E5D-922F-033A4D2F2CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
